--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260707.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260707.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>156,955</t>
+          <t>156,305</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.69%</t>
+          <t>26.82%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>17,935</t>
+          <t>17,835</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.39%</t>
+          <t>8.89%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>113,700</t>
+          <t>113,200</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.43%</t>
+          <t>7.42%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>58,095</t>
+          <t>57,795</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.58%</t>
+          <t>6.17%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>138,465</t>
+          <t>137,755</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>5.64%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>68,110</t>
+          <t>67,760</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.47%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>74,675</t>
+          <t>74,295</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>51,465</t>
+          <t>51,205</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
@@ -814,51 +814,51 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>22,575</t>
+          <t>20,783</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>20,893</t>
+          <t>22,455</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>35,960</t>
+          <t>35,780</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>58,265</t>
+          <t>57,965</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -919,100 +919,100 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>23,115</t>
+          <t>22,995</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>9,090</t>
+          <t>87,355</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>87,755</t>
+          <t>30,178</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>22,280</t>
+          <t>9,090</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>30,328</t>
+          <t>22,170</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>41,210</t>
+          <t>41,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
@@ -1051,78 +1051,78 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>67,598</t>
+          <t>67,258</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>10,966</t>
+          <t>24,158</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>13,351</t>
+          <t>10,866</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>24,278</t>
+          <t>13,251</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,045</t>
+          <t>20,935</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>144,355</t>
+          <t>143,615</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1183,56 +1183,56 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,201</t>
+          <t>18,101</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>22,547</t>
+          <t>42,540</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>42,760</t>
+          <t>22,387</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,405</t>
+          <t>13,305</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>49,190</t>
+          <t>48,940</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>956,916</t>
+          <t>1,317,683</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>12,829,200</t>
+          <t>22,471,200</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>360,767</t>
+          <t>1,007,703</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
